--- a/partner_results/jade/ClassMissingGermanLabel_jade.xlsx
+++ b/partner_results/jade/ClassMissingGermanLabel_jade.xlsx
@@ -446,18 +446,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>exterior orientation [jade]</t>
+          <t>camera coordinate system [jade]</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>relational quality</t>
+          <t>information content entity</t>
         </is>
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
-          <t>"The exterior orientation consists of six parameters which describe the spatial position and orientation of the camera coordinate system with respect to the global object coordinate system" (Luhmann et al. 2020: 277)</t>
+          <t>"The camera coordinate system has its origin at the perspective centre of the image. It is further defined by reference features fixed in the camera (fiducial marks, réseau, sensor system). It can therefore be reconstructed from the image and related to an image measuring device" (Luhmann et al. 2020: 278)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -484,18 +484,18 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>camera coordinate system [jade]</t>
+          <t>bundle adjustment method [jade]</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>information content entity</t>
+          <t>plan specification</t>
         </is>
       </c>
       <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>"The camera coordinate system has its origin at the perspective centre of the image. It is further defined by reference features fixed in the camera (fiducial marks, réseau, sensor system). It can therefore be reconstructed from the image and related to an image measuring device" (Luhmann et al. 2020: 278)</t>
+          <t>"Bundle adjustment [...] is a method for the simultaneous numerical fit of an unlimited number of spatially distributed images (bundles of rays). It makes use of photogrammetric observations (measured image points), survey observations and an object coordinate system. Using tie points, single images are merged into a global model in which the object surface can be reconstructed in three dimensions." (Luhmann et al. 2020: 349f.)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -503,18 +503,18 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>bundle adjustment method [jade]</t>
+          <t>exterior orientation [jade]</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>plan specification</t>
+          <t>relational quality</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>"Bundle adjustment [...] is a method for the simultaneous numerical fit of an unlimited number of spatially distributed images (bundles of rays). It makes use of photogrammetric observations (measured image points), survey observations and an object coordinate system. Using tie points, single images are merged into a global model in which the object surface can be reconstructed in three dimensions." (Luhmann et al. 2020: 349f.)</t>
+          <t>"The exterior orientation consists of six parameters which describe the spatial position and orientation of the camera coordinate system with respect to the global object coordinate system" (Luhmann et al. 2020: 277)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
